--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2019_atacama_provincial.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2019_atacama_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 22:43</t>
+    <t xml:space="preserve">2026-10-05 05:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
